--- a/artfynd/A 47048-2024 artfynd.xlsx
+++ b/artfynd/A 47048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120729317</v>
+        <v>120755112</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>885368</v>
+        <v>885427</v>
       </c>
       <c r="R2" t="n">
-        <v>7404260</v>
+        <v>7404232</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,6 +748,11 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,27 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120729314</v>
+        <v>120755113</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>885362</v>
+        <v>885348</v>
       </c>
       <c r="R3" t="n">
-        <v>7404453</v>
+        <v>7404342</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,27 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120729315</v>
+        <v>120755114</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>885479</v>
+        <v>885417</v>
       </c>
       <c r="R4" t="n">
-        <v>7404286</v>
+        <v>7404355</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -957,6 +947,11 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -969,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120729316</v>
+        <v>120755092</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>885408</v>
+        <v>885422</v>
       </c>
       <c r="R5" t="n">
-        <v>7404296</v>
+        <v>7404354</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1071,49 +1061,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120755124</v>
+        <v>120755108</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>885495</v>
+        <v>885529</v>
       </c>
       <c r="R6" t="n">
-        <v>7404244</v>
+        <v>7404239</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,37 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120755111</v>
+        <v>120755109</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>885347</v>
+        <v>885475</v>
       </c>
       <c r="R7" t="n">
-        <v>7404452</v>
+        <v>7404277</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1261,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,37 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120755093</v>
+        <v>120755089</v>
       </c>
       <c r="B8" t="n">
-        <v>91365</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1588</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>885403</v>
+        <v>885438</v>
       </c>
       <c r="R8" t="n">
-        <v>7404240</v>
+        <v>7404334</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120755102</v>
+        <v>120755093</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>885424</v>
+        <v>885403</v>
       </c>
       <c r="R9" t="n">
-        <v>7404231</v>
+        <v>7404240</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1496,37 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120755089</v>
+        <v>120755094</v>
       </c>
       <c r="B10" t="n">
-        <v>90848</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>885438</v>
+        <v>885480</v>
       </c>
       <c r="R10" t="n">
-        <v>7404334</v>
+        <v>7404462</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1598,37 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120755097</v>
+        <v>120755090</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>885408</v>
+        <v>885442</v>
       </c>
       <c r="R11" t="n">
-        <v>7404251</v>
+        <v>7404358</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1674,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>avbarkad gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,50 +1655,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120755095</v>
+        <v>120729314</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>885481</v>
+        <v>885362</v>
       </c>
       <c r="R12" t="n">
-        <v>7404425</v>
+        <v>7404453</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1783,11 +1728,6 @@
           <t>2024-10-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3 avbarkade granar</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1800,62 +1740,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120755094</v>
+        <v>120729315</v>
       </c>
       <c r="B13" t="n">
-        <v>91365</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>885480</v>
+        <v>885479</v>
       </c>
       <c r="R13" t="n">
-        <v>7404462</v>
+        <v>7404286</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1902,31 +1837,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120755126</v>
+        <v>120729316</v>
       </c>
       <c r="B14" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1950,14 +1880,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>885378</v>
+        <v>885408</v>
       </c>
       <c r="R14" t="n">
-        <v>7404262</v>
+        <v>7404296</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,31 +1934,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120755121</v>
+        <v>120729317</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2052,14 +1977,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>885453</v>
+        <v>885368</v>
       </c>
       <c r="R15" t="n">
-        <v>7404367</v>
+        <v>7404260</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2106,49 +2031,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120755106</v>
+        <v>120755121</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>885471</v>
+        <v>885453</v>
       </c>
       <c r="R16" t="n">
-        <v>7404325</v>
+        <v>7404367</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2220,37 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120755092</v>
+        <v>120755122</v>
       </c>
       <c r="B17" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>885422</v>
+        <v>885414</v>
       </c>
       <c r="R17" t="n">
-        <v>7404354</v>
+        <v>7404409</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2322,15 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120755118</v>
+        <v>120755123</v>
       </c>
       <c r="B18" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>885457</v>
+        <v>885503</v>
       </c>
       <c r="R18" t="n">
-        <v>7404338</v>
+        <v>7404228</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2424,37 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120755107</v>
+        <v>120755124</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>885407</v>
+        <v>885495</v>
       </c>
       <c r="R19" t="n">
-        <v>7404282</v>
+        <v>7404244</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2526,37 +2431,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120755090</v>
+        <v>120755125</v>
       </c>
       <c r="B20" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>885442</v>
+        <v>885440</v>
       </c>
       <c r="R20" t="n">
-        <v>7404358</v>
+        <v>7404320</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,19 +2528,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120755123</v>
+        <v>120755126</v>
       </c>
       <c r="B21" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2668,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>885503</v>
+        <v>885378</v>
       </c>
       <c r="R21" t="n">
-        <v>7404228</v>
+        <v>7404262</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2730,37 +2625,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120755112</v>
+        <v>120755127</v>
       </c>
       <c r="B22" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>885427</v>
+        <v>885350</v>
       </c>
       <c r="R22" t="n">
-        <v>7404232</v>
+        <v>7404252</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2806,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,15 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120755127</v>
+        <v>120755116</v>
       </c>
       <c r="B23" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>885350</v>
+        <v>885453</v>
       </c>
       <c r="R23" t="n">
-        <v>7404252</v>
+        <v>7404210</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2939,50 +2819,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120755125</v>
+        <v>120729308</v>
       </c>
       <c r="B24" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>885440</v>
+        <v>885464</v>
       </c>
       <c r="R24" t="n">
-        <v>7404320</v>
+        <v>7404217</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3029,49 +2904,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120755122</v>
+        <v>120755100</v>
       </c>
       <c r="B25" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>885414</v>
+        <v>885454</v>
       </c>
       <c r="R25" t="n">
-        <v>7404409</v>
+        <v>7404224</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3143,15 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120755108</v>
+        <v>120755101</v>
       </c>
       <c r="B26" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>885529</v>
+        <v>885458</v>
       </c>
       <c r="R26" t="n">
-        <v>7404239</v>
+        <v>7404217</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3245,15 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120755103</v>
+        <v>120755102</v>
       </c>
       <c r="B27" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>885534</v>
+        <v>885424</v>
       </c>
       <c r="R27" t="n">
-        <v>7404434</v>
+        <v>7404231</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3347,37 +3207,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120755110</v>
+        <v>120755103</v>
       </c>
       <c r="B28" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>885187</v>
+        <v>885534</v>
       </c>
       <c r="R28" t="n">
-        <v>7404490</v>
+        <v>7404434</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3423,11 +3278,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3457,12 +3307,7 @@
         <v>120755105</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,37 +3401,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120755114</v>
+        <v>120755106</v>
       </c>
       <c r="B30" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>885417</v>
+        <v>885471</v>
       </c>
       <c r="R30" t="n">
-        <v>7404355</v>
+        <v>7404325</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3632,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3663,15 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120755109</v>
+        <v>120755107</v>
       </c>
       <c r="B31" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,21 +3509,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>885475</v>
+        <v>885407</v>
       </c>
       <c r="R31" t="n">
-        <v>7404277</v>
+        <v>7404282</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3765,32 +3595,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120755096</v>
+        <v>120755110</v>
       </c>
       <c r="B32" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3805,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>885438</v>
+        <v>885187</v>
       </c>
       <c r="R32" t="n">
-        <v>7404472</v>
+        <v>7404490</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3845,7 +3670,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3869,6 +3694,608 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120755111</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>885347</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7404452</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120755095</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>885481</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7404425</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 avbarkade granar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120755096</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>885438</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7404472</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120755097</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>885408</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7404251</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120755117</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>885459</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7404218</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120755118</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>885457</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7404338</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47048-2024 artfynd.xlsx
+++ b/artfynd/A 47048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755112</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755092</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755089</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755093</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755090</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729314</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729315</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729316</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729317</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755121</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755122</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755123</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755124</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755125</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755126</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755127</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755116</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729308</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755100</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755101</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755102</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755103</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3398,6 +3538,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755105</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755106</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3592,6 +3742,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755107</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3694,6 +3849,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755110</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3796,6 +3956,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755111</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3898,6 +4063,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755095</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4000,6 +4170,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755096</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4102,6 +4277,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755097</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4199,6 +4379,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755117</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4296,8 +4481,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>